--- a/artfynd/A 25718-2025 artfynd.xlsx
+++ b/artfynd/A 25718-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129035110</v>
       </c>
       <c r="B2" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>129035109</v>
       </c>
       <c r="B3" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>129034879</v>
       </c>
       <c r="B4" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 25718-2025 artfynd.xlsx
+++ b/artfynd/A 25718-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129035110</v>
       </c>
       <c r="B2" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>129035109</v>
       </c>
       <c r="B3" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>129034879</v>
       </c>
       <c r="B4" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 25718-2025 artfynd.xlsx
+++ b/artfynd/A 25718-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129035110</v>
       </c>
       <c r="B2" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>129035109</v>
       </c>
       <c r="B3" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>129034879</v>
       </c>
       <c r="B4" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 25718-2025 artfynd.xlsx
+++ b/artfynd/A 25718-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129035110</v>
       </c>
       <c r="B2" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>129035109</v>
       </c>
       <c r="B3" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>129034879</v>
       </c>
       <c r="B4" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 25718-2025 artfynd.xlsx
+++ b/artfynd/A 25718-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129035110</v>
       </c>
       <c r="B2" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>129035109</v>
       </c>
       <c r="B3" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>129034879</v>
       </c>
       <c r="B4" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 25718-2025 artfynd.xlsx
+++ b/artfynd/A 25718-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129035110</v>
       </c>
       <c r="B2" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>129035109</v>
       </c>
       <c r="B3" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>129034879</v>
       </c>
       <c r="B4" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 25718-2025 artfynd.xlsx
+++ b/artfynd/A 25718-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129035110</v>
       </c>
       <c r="B2" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>129035109</v>
       </c>
       <c r="B3" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>129034879</v>
       </c>
       <c r="B4" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 25718-2025 artfynd.xlsx
+++ b/artfynd/A 25718-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129035110</v>
       </c>
       <c r="B2" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>129035109</v>
       </c>
       <c r="B3" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>129034879</v>
       </c>
       <c r="B4" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 25718-2025 artfynd.xlsx
+++ b/artfynd/A 25718-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129035110</v>
       </c>
       <c r="B2" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>129035109</v>
       </c>
       <c r="B3" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>129034879</v>
       </c>
       <c r="B4" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 25718-2025 artfynd.xlsx
+++ b/artfynd/A 25718-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129035110</v>
       </c>
       <c r="B2" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>129035109</v>
       </c>
       <c r="B3" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>129034879</v>
       </c>
       <c r="B4" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 25718-2025 artfynd.xlsx
+++ b/artfynd/A 25718-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129035110</v>
       </c>
       <c r="B2" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>129035109</v>
       </c>
       <c r="B3" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>129034879</v>
       </c>
       <c r="B4" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 25718-2025 artfynd.xlsx
+++ b/artfynd/A 25718-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129035110</v>
       </c>
       <c r="B2" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>129035109</v>
       </c>
       <c r="B3" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>129034879</v>
       </c>
       <c r="B4" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 25718-2025 artfynd.xlsx
+++ b/artfynd/A 25718-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129035110</v>
       </c>
       <c r="B2" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>129035109</v>
       </c>
       <c r="B3" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>129034879</v>
       </c>
       <c r="B4" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
